--- a/data/output/evaluasi_15.xlsx
+++ b/data/output/evaluasi_15.xlsx
@@ -8,9 +8,17 @@
   </bookViews>
   <sheets>
     <sheet name="1500" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="1507" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="1503" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="1506" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="1502" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="1571" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="1572" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="1505" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="1501" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="1503" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="1507" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="1509" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="1504" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="1506" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="1508" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,7 +486,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-10.18922379658959</v>
+        <v>-28.6958842079376</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -487,7 +495,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -502,20 +510,20 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q2-25</t>
+          <t>q1-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>95.66798975631772</v>
+        <v>-2.569168453480488</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhb_pi_q2-25</t>
+          <t>q-to-q_pdrb_q1-25 vs q-to-q_pdrb_q1-25.1</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,3 point)</t>
         </is>
       </c>
     </row>
@@ -530,20 +538,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>46.99544971754445</v>
+        <v>4.943419444654851</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>adhk_pi_q1-25</t>
+          <t>q-to-q_pdrb_q2-25 vs q-to-q_pdrb_q2-25.1</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,3 point)</t>
         </is>
       </c>
     </row>
@@ -562,16 +570,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>90.65380396065561</v>
+        <v>6.218008515157873</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>adhk_pi_q2-25</t>
+          <t>q-to-q_pklnprt_q2-25 vs q-to-q_pklnprt_q2-25.1</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -590,16 +598,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.3933146504178661</v>
+        <v>32.80462522286963</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>distribusi_pi_q2-25 vs distribusi_pi_q2-25.1</t>
+          <t>q-to-q_pkp_q2-25 vs q-to-q_pkp_q2-25.1</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Distribusi lebih dari +- 20 persen</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -614,20 +622,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>q2-25</t>
+          <t>q1-25</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2.317870455878917</v>
+        <v>-14.49473459304559</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>c-to-c_pklnprt_q2-25 vs c-to-c_pklnprt_q2-25.1</t>
+          <t>q-to-q_pmtb_q1-25 vs q-to-q_pmtb_q1-25.1</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -642,20 +650,466 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>4.671875929905641</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q3-25 vs y-on-y_pdrb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,01 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>15</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Jambi</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>q1-25</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>0.7001615568766913</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>implisit_y-on-y_pklnprt_q1-25 vs implisit_y-on-y_pklnprt_q1-25.1</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+      <c r="D9" t="n">
+        <v>-6.182489587590513</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q1-25 vs y-on-y_pklnprt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>15</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Jambi</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2.281439269584808</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q2-25 vs y-on-y_pmtb_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>15</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Jambi</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-6.182489587590513</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q1-25 vs c-to-c_pklnprt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Jambi</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>4.185164933721927</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q3-25 vs implisit_y-on-y_pdrb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1504</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Batang Hari</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>11.99210120055613</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1504</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Batang Hari</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1.680831732566846</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1504</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Batang Hari</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-2.914097663490246</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1504</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Batang Hari</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>16.37761479714311</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q3-25_prov vs implisit_y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1506</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Tanjung Jabung Timur</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.01454902239390395</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1508</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Tebo</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.9572946802953453</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1508</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Tebo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.6731363849746407</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -670,7 +1124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -707,85 +1161,113 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1507</v>
+        <v>1502</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Tanjung Jabung Barat</t>
+          <t>Kabupaten Merangin</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-3765.334401009</v>
+        <v>39150.29907861368</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_pi_q1-25_ril vs adhb_pi_q1-25_rev</t>
+          <t>adhb_pi_q2-25_ril vs adhb_pi_q2-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Nilai revisi lebih dari (+-30%) dari nilai rilis</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1507</v>
+        <v>1502</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Tanjung Jabung Barat</t>
+          <t>Kabupaten Merangin</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-1670.331229352</v>
+        <v>22465.64986321412</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhk_pi_q1-25_ril vs adhk_pi_q1-25_rev</t>
+          <t>adhk_pi_q2-25_ril vs adhk_pi_q2-25_rev</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Nilai revisi lebih dari (+-30%) dari nilai rilis</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1507</v>
+        <v>1502</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Tanjung Jabung Barat</t>
+          <t>Kabupaten Merangin</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.01104164067728227</v>
+        <v>0.2478522728295967</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
+          <t>sog_y-on-y_pi_q2-25_ril vs sog_y-on-y_pi_q2-25_rev</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1502</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Merangin</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-10.7295050567039</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -800,7 +1282,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -837,113 +1319,197 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1503</v>
+        <v>1571</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Sarolangun</t>
+          <t>Kota Jambi</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3.024634786246782</v>
+        <v>36.5100962513505</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>y-on-y_pmtb_q1-25_ril vs y-on-y_pmtb_q1-25_rev</t>
+          <t>q-to-q_pkp_q2-25_ril vs q-to-q_pkp_q2-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1503</v>
+        <v>1571</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Sarolangun</t>
+          <t>Kota Jambi</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3.024634786246782</v>
+        <v>8.712863846641723</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>c-to-c_pmtb_q1-25_ril vs c-to-c_pmtb_q1-25_rev</t>
+          <t>y-on-y_pklnprt_q2-25_ril vs y-on-y_pklnprt_q2-25_rev</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1503</v>
+        <v>1571</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Sarolangun</t>
+          <t>Kota Jambi</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.075916004535279</v>
+        <v>-30.51751203232513</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pmtb_q1-25_ril vs sog_y-on-y_pmtb_q1-25_rev</t>
+          <t>y-on-y_pkp_q2-25_ril vs y-on-y_pkp_q2-25_rev</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1503</v>
+        <v>1571</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kabupaten Sarolangun</t>
+          <t>Kota Jambi</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.006153727907399441</v>
+        <v>-20.1825688210826</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>sog_y-on-y_net_ekspor_q1-25_ril vs sog_y-on-y_net_ekspor_q1-25_rev</t>
+          <t>c-to-c_pkp_q2-25_ril vs c-to-c_pkp_q2-25_rev</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1571</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Jambi</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2.767324678047889</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1571</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Jambi</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1.959561937333841</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1571</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kota Jambi</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-12.87121711789582</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -958,6 +1524,638 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1572</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Sungai Penuh</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>7.932589838029156</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q1-25_ril vs y-on-y_pkp_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1572</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Sungai Penuh</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>7.932589838029156</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q1-25_ril vs c-to-c_pkp_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1572</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Sungai Penuh</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>19.27643333128549</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1572</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Sungai Penuh</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>11.06651118643296</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1572</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Sungai Penuh</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.9230024600737026</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1572</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Sungai Penuh</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.06026793704697136</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1572</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kota Sungai Penuh</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-2.426998598208117</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1505</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Muaro Jambi</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2.485924757025903</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q2-25_ril vs sog_q_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1505</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Muaro Jambi</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-3.104867921940296</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1505</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Muaro Jambi</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-6.030027700935046</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1505</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Muaro Jambi</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-1.993215411161168</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1501</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Kerinci</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>30.09999504794149</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1501</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Kerinci</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>11.17125798913574</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1501</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Kerinci</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-2.714888332465758</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1501</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Kerinci</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-1.841543919903203</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q3-25_prov vs implisit_q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1503</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Sarolangun</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>13.89767233373039</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -995,141 +2193,327 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Tanjung Jabung Timur</t>
+          <t>Kabupaten Tanjung Jabung Barat</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.2184057532791685</v>
+        <v>14.38940991444835</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pklnprt_q1-25_ril vs implisit_q-to-q_pklnprt_q1-25_rev</t>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Tanjung Jabung Timur</t>
+          <t>Kabupaten Tanjung Jabung Barat</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.670325428980923</v>
+        <v>18.25080960997531</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkp_q1-25_ril vs implisit_q-to-q_pkp_q1-25_rev</t>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Tanjung Jabung Timur</t>
+          <t>Kabupaten Tanjung Jabung Barat</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.3492948874530488</v>
+        <v>0.2285698885994077</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>implisit_y-on-y_pklnprt_q1-25_ril vs implisit_y-on-y_pklnprt_q1-25_rev</t>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kabupaten Tanjung Jabung Timur</t>
+          <t>Kabupaten Tanjung Jabung Barat</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.192908845199732</v>
+        <v>3.384810212966442</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>sog_q_net_ekspor_q1-25_ril vs sog_q_net_ekspor_q1-25_rev</t>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kabupaten Tanjung Jabung Timur</t>
+          <t>Kabupaten Tanjung Jabung Barat</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.9480081071463551</v>
+        <v>6.882968638767192</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>sog_y-on-y_net_ekspor_q1-25_ril vs sog_y-on-y_net_ekspor_q1-25_rev</t>
+          <t>implisit_y-on-y_pdrb_q3-25_prov vs implisit_y-on-y_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1509</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Bungo</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>11.36849224958386</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1509</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Bungo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-5.441024730694028</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1509</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Bungo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-12.75859172291642</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1509</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Bungo</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.3981215554673492</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1509</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Bungo</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.3627212033377277</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q3-25_prov vs implisit_y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>

--- a/data/output/evaluasi_15.xlsx
+++ b/data/output/evaluasi_15.xlsx
@@ -523,7 +523,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,3 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -551,7 +551,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,3 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -579,7 +579,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -691,7 +691,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -747,7 +747,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -775,7 +775,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
